--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_tarapaca_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_tarapaca_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:10</t>
+    <t xml:space="preserve">2026-09-29 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_tarapaca_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_tarapaca_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:06</t>
+    <t xml:space="preserve">2026-09-29 18:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -501,10 +501,10 @@
         <v>-11.15</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>30.19</v>
+        <v>30.2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>41.34</v>
+        <v>41.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_tarapaca_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_tarapaca_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:37</t>
+    <t xml:space="preserve">2026-10-05 04:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
